--- a/diseases/d240/2020-2025.xlsx
+++ b/diseases/d240/2020-2025.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -25365,7 +25365,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -35353,7 +35353,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -39666,7 +39666,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -41028,7 +41028,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -42617,7 +42617,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -45568,7 +45568,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -46930,7 +46930,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -49881,7 +49881,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -51243,7 +51243,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -52605,7 +52605,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -53059,7 +53059,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -53513,7 +53513,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -53967,7 +53967,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -54421,7 +54421,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -54875,7 +54875,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -56237,7 +56237,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -56691,7 +56691,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -57599,7 +57599,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -58053,7 +58053,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -58507,7 +58507,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -58961,7 +58961,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -59415,7 +59415,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -59869,7 +59869,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -60323,7 +60323,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -60777,7 +60777,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -61231,7 +61231,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -61685,7 +61685,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -62139,7 +62139,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -62593,7 +62593,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -63047,7 +63047,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -63501,7 +63501,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -63955,7 +63955,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -64863,7 +64863,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -65317,7 +65317,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -65771,7 +65771,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -66225,7 +66225,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -66679,7 +66679,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -67133,7 +67133,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -67587,7 +67587,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -68041,7 +68041,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -68495,7 +68495,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">

--- a/diseases/d240/2020-2025.xlsx
+++ b/diseases/d240/2020-2025.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -25365,7 +25365,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -31040,7 +31040,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -35353,7 +35353,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -39666,7 +39666,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -41028,7 +41028,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -42617,7 +42617,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -45568,7 +45568,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -46930,7 +46930,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -49881,7 +49881,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -51243,7 +51243,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -52605,7 +52605,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -53059,7 +53059,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -53513,7 +53513,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -53967,7 +53967,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -54421,7 +54421,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -54875,7 +54875,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -56237,7 +56237,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -56691,7 +56691,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -57599,7 +57599,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -58053,7 +58053,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -58507,7 +58507,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -58961,7 +58961,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -59415,7 +59415,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -59869,7 +59869,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -60323,7 +60323,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -60777,7 +60777,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -61231,7 +61231,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -61685,7 +61685,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -62139,7 +62139,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -62593,7 +62593,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -63047,7 +63047,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -63501,7 +63501,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -63955,7 +63955,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -64863,7 +64863,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -65317,7 +65317,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -65771,7 +65771,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -66225,7 +66225,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -66679,7 +66679,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -67133,7 +67133,7 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN294" t="b">
@@ -67587,7 +67587,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -68041,7 +68041,7 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN298" t="b">
@@ -68495,7 +68495,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">
